--- a/Assets/ArtRes/Excel/灵居配置表.xlsx
+++ b/Assets/ArtRes/Excel/灵居配置表.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="99">
   <si>
     <t>id</t>
   </si>
@@ -40,7 +40,7 @@
     <t>rarity</t>
   </si>
   <si>
-    <t>energy</t>
+    <t>cost</t>
   </si>
   <si>
     <t>atk</t>
@@ -73,6 +73,9 @@
     <t>prefabName</t>
   </si>
   <si>
+    <t>missRate</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -128,6 +131,9 @@
   </si>
   <si>
     <t>预设体路径</t>
+  </si>
+  <si>
+    <t>闪避率（0-1）</t>
   </si>
   <si>
     <t>工具箱</t>
@@ -174,7 +180,7 @@
     <t>[攻击]:如果对方是没有格挡值的非boss灵居，直接秒杀</t>
   </si>
   <si>
-    <t>铝罐</t>
+    <t>罐头</t>
   </si>
   <si>
     <t>[装甲4]:受到的伤害减4</t>
@@ -328,6 +334,15 @@
   </si>
   <si>
     <t>[攻击]:当攻击的对象有点燃效果时，将点燃效果加倍</t>
+  </si>
+  <si>
+    <t>打火机</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[穿透攻击]
+[攻击]：对攻击到的敌人施加5层[点燃]效果
+[点燃*n]：每回合掉n点血量，回合结束时层数减半
+</t>
   </si>
 </sst>
 </file>
@@ -972,7 +987,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -995,6 +1010,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1308,7 +1326,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N97"/>
+  <dimension ref="A1:O102"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="9" max="9" width="26.2727272727273" customWidth="1"/>
@@ -1318,7 +1336,7 @@
     <col min="14" max="14" width="11.2727272727273" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1361,54 +1379,60 @@
       <c r="N1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="E2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="1" t="s">
+      <c r="J2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K2" s="1" t="s">
+      <c r="M2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N2" t="s">
         <v>16</v>
       </c>
-      <c r="L2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -1423,48 +1447,51 @@
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
-    <row r="4" ht="98" customHeight="1" spans="1:14">
+    <row r="4" ht="98" customHeight="1" spans="1:15">
       <c r="A4" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="N4" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="O4" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="5" ht="42" spans="1:13">
@@ -1472,7 +1499,7 @@
         <v>10</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C5" s="1">
         <v>3</v>
@@ -1493,7 +1520,7 @@
         <v>20</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J5" s="1"/>
       <c r="K5" s="1">
@@ -1507,7 +1534,7 @@
         <v>11</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C6" s="1">
         <v>3</v>
@@ -1528,7 +1555,7 @@
         <v>20</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J6" s="1"/>
       <c r="K6" s="1">
@@ -1542,7 +1569,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C7" s="1">
         <v>3</v>
@@ -1563,7 +1590,7 @@
         <v>20</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J7" s="1"/>
       <c r="K7" s="1">
@@ -1577,7 +1604,7 @@
         <v>20</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C8" s="1">
         <v>2</v>
@@ -1598,7 +1625,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J8" s="1">
         <v>3</v>
@@ -1614,7 +1641,7 @@
         <v>21</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C9" s="1">
         <v>2</v>
@@ -1635,7 +1662,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J9" s="1">
         <v>3</v>
@@ -1651,7 +1678,7 @@
         <v>22</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C10" s="1">
         <v>2</v>
@@ -1672,7 +1699,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J10" s="1">
         <v>3</v>
@@ -1688,7 +1715,7 @@
         <v>30</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C11" s="1">
         <v>1</v>
@@ -1709,7 +1736,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J11" s="1"/>
       <c r="K11" s="1">
@@ -1723,7 +1750,7 @@
         <v>31</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C12" s="1">
         <v>1</v>
@@ -1744,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J12" s="1"/>
       <c r="K12" s="1">
@@ -1758,7 +1785,7 @@
         <v>32</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C13" s="1">
         <v>1</v>
@@ -1779,7 +1806,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J13" s="1"/>
       <c r="K13" s="1">
@@ -1793,7 +1820,7 @@
         <v>40</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C14" s="1">
         <v>2</v>
@@ -1810,7 +1837,7 @@
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
       <c r="I14" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J14" s="1"/>
       <c r="K14" s="1">
@@ -1824,7 +1851,7 @@
         <v>41</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C15" s="1">
         <v>2</v>
@@ -1841,7 +1868,7 @@
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
       <c r="I15" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J15" s="1"/>
       <c r="K15" s="1">
@@ -1855,7 +1882,7 @@
         <v>42</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C16" s="1">
         <v>2</v>
@@ -1872,7 +1899,7 @@
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J16" s="1"/>
       <c r="K16" s="1">
@@ -1886,7 +1913,7 @@
         <v>50</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C17" s="1">
         <v>4</v>
@@ -1903,7 +1930,7 @@
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
       <c r="I17" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J17" s="1"/>
       <c r="K17" s="1">
@@ -1917,7 +1944,7 @@
         <v>51</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C18" s="1">
         <v>4</v>
@@ -1934,7 +1961,7 @@
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
       <c r="I18" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J18" s="1"/>
       <c r="K18" s="1">
@@ -1948,7 +1975,7 @@
         <v>52</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C19" s="1">
         <v>4</v>
@@ -1965,7 +1992,7 @@
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
       <c r="I19" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J19" s="1"/>
       <c r="K19" s="1">
@@ -1979,7 +2006,7 @@
         <v>60</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C20" s="4">
         <v>3</v>
@@ -2000,7 +2027,7 @@
         <v>0</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J20" s="1"/>
       <c r="K20" s="1">
@@ -2014,7 +2041,7 @@
         <v>61</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C21" s="1">
         <v>3</v>
@@ -2035,7 +2062,7 @@
         <v>0</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J21" s="1"/>
       <c r="K21" s="1">
@@ -2049,7 +2076,7 @@
         <v>62</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C22" s="1">
         <v>3</v>
@@ -2070,7 +2097,7 @@
         <v>0</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J22" s="1"/>
       <c r="K22" s="1">
@@ -2084,7 +2111,7 @@
         <v>70</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C23" s="1">
         <v>5</v>
@@ -2105,7 +2132,7 @@
         <v>0</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J23" s="1"/>
       <c r="K23" s="1">
@@ -2119,7 +2146,7 @@
         <v>71</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C24" s="1">
         <v>5</v>
@@ -2140,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J24" s="1"/>
       <c r="K24" s="1">
@@ -2154,7 +2181,7 @@
         <v>72</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C25" s="1">
         <v>5</v>
@@ -2175,7 +2202,7 @@
         <v>0</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J25" s="1"/>
       <c r="K25" s="1">
@@ -2189,7 +2216,7 @@
         <v>80</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C26" s="1">
         <v>1</v>
@@ -2210,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J26" s="1"/>
       <c r="K26" s="1">
@@ -2224,7 +2251,7 @@
         <v>81</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C27" s="1">
         <v>1</v>
@@ -2245,7 +2272,7 @@
         <v>0</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J27" s="1"/>
       <c r="K27" s="1">
@@ -2259,7 +2286,7 @@
         <v>82</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C28" s="1">
         <v>1</v>
@@ -2280,7 +2307,7 @@
         <v>0</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J28" s="1"/>
       <c r="K28" s="1">
@@ -2294,7 +2321,7 @@
         <v>90</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C29" s="1">
         <v>1</v>
@@ -2327,7 +2354,7 @@
         <v>91</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C30" s="1">
         <v>1</v>
@@ -2360,7 +2387,7 @@
         <v>92</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C31" s="1">
         <v>1</v>
@@ -2393,7 +2420,7 @@
         <v>100</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
@@ -2414,7 +2441,7 @@
         <v>101</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
@@ -2435,7 +2462,7 @@
         <v>102</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
@@ -2456,7 +2483,7 @@
         <v>110</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C35" s="5">
         <v>1</v>
@@ -2477,7 +2504,7 @@
         <v>0</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="J35" s="1"/>
       <c r="K35" s="1">
@@ -2491,7 +2518,7 @@
         <v>120</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C36" s="5">
         <v>1</v>
@@ -2512,7 +2539,7 @@
         <v>0</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J36" s="1"/>
       <c r="K36" s="1">
@@ -2526,7 +2553,7 @@
         <v>130</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C37" s="5">
         <v>1</v>
@@ -2547,7 +2574,7 @@
         <v>0</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J37" s="1"/>
       <c r="K37" s="1">
@@ -2561,7 +2588,7 @@
         <v>140</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C38" s="6">
         <v>2</v>
@@ -2582,7 +2609,7 @@
         <v>0</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
@@ -2594,7 +2621,7 @@
         <v>141</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C39" s="6">
         <v>2</v>
@@ -2615,7 +2642,7 @@
         <v>0</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
@@ -2627,7 +2654,7 @@
         <v>142</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C40" s="6">
         <v>2</v>
@@ -2648,7 +2675,7 @@
         <v>0</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
@@ -2660,7 +2687,7 @@
         <v>150</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C41" s="5">
         <v>3</v>
@@ -2681,7 +2708,7 @@
         <v>50</v>
       </c>
       <c r="I41" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J41" s="1"/>
       <c r="K41" s="1"/>
@@ -2693,7 +2720,7 @@
         <v>151</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C42" s="5">
         <v>3</v>
@@ -2714,7 +2741,7 @@
         <v>50</v>
       </c>
       <c r="I42" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
@@ -2726,7 +2753,7 @@
         <v>152</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C43" s="5">
         <v>3</v>
@@ -2747,7 +2774,7 @@
         <v>50</v>
       </c>
       <c r="I43" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J43" s="1"/>
       <c r="K43" s="1"/>
@@ -2759,7 +2786,7 @@
         <v>160</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C44" s="4">
         <v>1</v>
@@ -2790,7 +2817,7 @@
         <v>161</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C45" s="4">
         <v>1</v>
@@ -2821,7 +2848,7 @@
         <v>162</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C46" s="4">
         <v>1</v>
@@ -2852,7 +2879,7 @@
         <v>170</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C47" s="5">
         <v>1</v>
@@ -2883,7 +2910,7 @@
         <v>171</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C48" s="5">
         <v>1</v>
@@ -2914,7 +2941,7 @@
         <v>172</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C49" s="5">
         <v>1</v>
@@ -2945,7 +2972,7 @@
         <v>180</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C50" s="5">
         <v>2</v>
@@ -2966,7 +2993,7 @@
         <v>0</v>
       </c>
       <c r="I50" s="4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J50" s="1"/>
       <c r="K50" s="1"/>
@@ -2978,7 +3005,7 @@
         <v>181</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C51" s="5">
         <v>2</v>
@@ -2999,7 +3026,7 @@
         <v>0</v>
       </c>
       <c r="I51" s="4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J51" s="1"/>
       <c r="K51" s="1"/>
@@ -3011,7 +3038,7 @@
         <v>182</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C52" s="5">
         <v>2</v>
@@ -3032,7 +3059,7 @@
         <v>0</v>
       </c>
       <c r="I52" s="4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
@@ -3044,7 +3071,7 @@
         <v>190</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C53" s="5">
         <v>4</v>
@@ -3065,7 +3092,7 @@
         <v>0</v>
       </c>
       <c r="I53" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="J53" s="1"/>
       <c r="K53" s="1"/>
@@ -3077,7 +3104,7 @@
         <v>191</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C54" s="5">
         <v>4</v>
@@ -3098,7 +3125,7 @@
         <v>0</v>
       </c>
       <c r="I54" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="J54" s="1"/>
       <c r="K54" s="1"/>
@@ -3110,7 +3137,7 @@
         <v>192</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C55" s="5">
         <v>4</v>
@@ -3131,7 +3158,7 @@
         <v>0</v>
       </c>
       <c r="I55" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="J55" s="1"/>
       <c r="K55" s="1"/>
@@ -3143,7 +3170,7 @@
         <v>200</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C56" s="4">
         <v>4</v>
@@ -3164,7 +3191,7 @@
         <v>0</v>
       </c>
       <c r="I56" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J56" s="1"/>
       <c r="K56" s="1"/>
@@ -3176,7 +3203,7 @@
         <v>201</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C57" s="4">
         <v>4</v>
@@ -3197,7 +3224,7 @@
         <v>0</v>
       </c>
       <c r="I57" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J57" s="1"/>
       <c r="K57" s="1"/>
@@ -3209,7 +3236,7 @@
         <v>202</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C58" s="4">
         <v>4</v>
@@ -3230,7 +3257,7 @@
         <v>0</v>
       </c>
       <c r="I58" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J58" s="1"/>
       <c r="K58" s="1"/>
@@ -3242,7 +3269,7 @@
         <v>210</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C59" s="5">
         <v>5</v>
@@ -3263,7 +3290,7 @@
         <v>50</v>
       </c>
       <c r="I59" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J59" s="1"/>
       <c r="K59" s="1"/>
@@ -3275,7 +3302,7 @@
         <v>211</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C60" s="5">
         <v>5</v>
@@ -3296,7 +3323,7 @@
         <v>50</v>
       </c>
       <c r="I60" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J60" s="1"/>
       <c r="K60" s="1"/>
@@ -3308,7 +3335,7 @@
         <v>212</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C61" s="5">
         <v>5</v>
@@ -3329,7 +3356,7 @@
         <v>50</v>
       </c>
       <c r="I61" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J61" s="1"/>
       <c r="K61" s="1"/>
@@ -3341,7 +3368,7 @@
         <v>220</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C62" s="5">
         <v>1</v>
@@ -3362,7 +3389,7 @@
         <v>0</v>
       </c>
       <c r="I62" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J62" s="1"/>
       <c r="K62" s="1"/>
@@ -3374,7 +3401,7 @@
         <v>221</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C63" s="5">
         <v>1</v>
@@ -3395,7 +3422,7 @@
         <v>0</v>
       </c>
       <c r="I63" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J63" s="1"/>
       <c r="K63" s="1"/>
@@ -3407,7 +3434,7 @@
         <v>222</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C64" s="5">
         <v>1</v>
@@ -3428,7 +3455,7 @@
         <v>0</v>
       </c>
       <c r="I64" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J64" s="1"/>
       <c r="K64" s="1"/>
@@ -3440,7 +3467,7 @@
         <v>230</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C65" s="5">
         <v>3</v>
@@ -3461,7 +3488,7 @@
         <v>10</v>
       </c>
       <c r="I65" s="4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J65" s="1"/>
       <c r="K65" s="1"/>
@@ -3473,7 +3500,7 @@
         <v>231</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C66" s="5">
         <v>3</v>
@@ -3494,7 +3521,7 @@
         <v>10</v>
       </c>
       <c r="I66" s="4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J66" s="1"/>
       <c r="K66" s="1"/>
@@ -3506,7 +3533,7 @@
         <v>232</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C67" s="5">
         <v>3</v>
@@ -3527,7 +3554,7 @@
         <v>10</v>
       </c>
       <c r="I67" s="4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J67" s="1"/>
       <c r="K67" s="1"/>
@@ -3539,7 +3566,7 @@
         <v>240</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C68" s="5">
         <v>2</v>
@@ -3560,7 +3587,7 @@
         <v>0</v>
       </c>
       <c r="I68" s="4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J68" s="1"/>
       <c r="K68" s="1"/>
@@ -3572,7 +3599,7 @@
         <v>241</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C69" s="5">
         <v>2</v>
@@ -3593,7 +3620,7 @@
         <v>0</v>
       </c>
       <c r="I69" s="4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J69" s="1"/>
       <c r="K69" s="1"/>
@@ -3605,7 +3632,7 @@
         <v>242</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C70" s="5">
         <v>2</v>
@@ -3626,7 +3653,7 @@
         <v>0</v>
       </c>
       <c r="I70" s="4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J70" s="1"/>
       <c r="K70" s="1"/>
@@ -3638,7 +3665,7 @@
         <v>250</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C71" s="4">
         <v>3</v>
@@ -3659,7 +3686,7 @@
         <v>20</v>
       </c>
       <c r="I71" s="4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="J71" s="1"/>
       <c r="K71" s="1"/>
@@ -3671,7 +3698,7 @@
         <v>251</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C72" s="4">
         <v>3</v>
@@ -3692,7 +3719,7 @@
         <v>20</v>
       </c>
       <c r="I72" s="4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="J72" s="1"/>
       <c r="K72" s="1"/>
@@ -3704,7 +3731,7 @@
         <v>252</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C73" s="4">
         <v>3</v>
@@ -3725,7 +3752,7 @@
         <v>20</v>
       </c>
       <c r="I73" s="4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="J73" s="1"/>
       <c r="K73" s="1"/>
@@ -3737,7 +3764,7 @@
         <v>260</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C74" s="4">
         <v>1</v>
@@ -3758,7 +3785,7 @@
         <v>0</v>
       </c>
       <c r="I74" s="4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="J74" s="1"/>
       <c r="K74" s="1"/>
@@ -3770,7 +3797,7 @@
         <v>261</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C75" s="4">
         <v>1</v>
@@ -3791,7 +3818,7 @@
         <v>0</v>
       </c>
       <c r="I75" s="4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="J75" s="1"/>
       <c r="K75" s="1"/>
@@ -3803,7 +3830,7 @@
         <v>262</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C76" s="4">
         <v>1</v>
@@ -3824,7 +3851,7 @@
         <v>0</v>
       </c>
       <c r="I76" s="4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="J76" s="1"/>
       <c r="K76" s="1"/>
@@ -3836,7 +3863,7 @@
         <v>270</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C77" s="4">
         <v>2</v>
@@ -3857,7 +3884,7 @@
         <v>0</v>
       </c>
       <c r="I77" s="4" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J77" s="1"/>
       <c r="K77" s="1"/>
@@ -3869,7 +3896,7 @@
         <v>271</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C78" s="4">
         <v>2</v>
@@ -3890,7 +3917,7 @@
         <v>0</v>
       </c>
       <c r="I78" s="4" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J78" s="1"/>
       <c r="K78" s="1"/>
@@ -3902,7 +3929,7 @@
         <v>272</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C79" s="4">
         <v>2</v>
@@ -3923,7 +3950,7 @@
         <v>0</v>
       </c>
       <c r="I79" s="4" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J79" s="1"/>
       <c r="K79" s="1"/>
@@ -3935,7 +3962,7 @@
         <v>280</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C80" s="4">
         <v>2</v>
@@ -3956,7 +3983,7 @@
         <v>0</v>
       </c>
       <c r="I80" s="4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J80" s="1"/>
       <c r="K80" s="1"/>
@@ -3968,7 +3995,7 @@
         <v>281</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C81" s="4">
         <v>2</v>
@@ -3989,7 +4016,7 @@
         <v>0</v>
       </c>
       <c r="I81" s="4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J81" s="1"/>
       <c r="K81" s="1"/>
@@ -4001,7 +4028,7 @@
         <v>282</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C82" s="4">
         <v>2</v>
@@ -4022,7 +4049,7 @@
         <v>0</v>
       </c>
       <c r="I82" s="4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J82" s="1"/>
       <c r="K82" s="1"/>
@@ -4034,7 +4061,7 @@
         <v>290</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C83" s="4">
         <v>3</v>
@@ -4055,7 +4082,7 @@
         <v>0</v>
       </c>
       <c r="I83" s="4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="J83" s="1"/>
       <c r="K83" s="1"/>
@@ -4067,7 +4094,7 @@
         <v>291</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C84" s="4">
         <v>3</v>
@@ -4088,7 +4115,7 @@
         <v>0</v>
       </c>
       <c r="I84" s="4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="J84" s="1"/>
       <c r="K84" s="1"/>
@@ -4100,7 +4127,7 @@
         <v>292</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C85" s="4">
         <v>3</v>
@@ -4121,7 +4148,7 @@
         <v>0</v>
       </c>
       <c r="I85" s="4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="J85" s="1"/>
       <c r="K85" s="1"/>
@@ -4133,7 +4160,7 @@
         <v>300</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C86" s="5">
         <v>5</v>
@@ -4154,7 +4181,7 @@
         <v>50</v>
       </c>
       <c r="I86" s="4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="J86" s="1"/>
       <c r="K86" s="1"/>
@@ -4166,7 +4193,7 @@
         <v>301</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C87" s="5">
         <v>5</v>
@@ -4187,7 +4214,7 @@
         <v>50</v>
       </c>
       <c r="I87" s="4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="J87" s="1"/>
       <c r="K87" s="1"/>
@@ -4199,7 +4226,7 @@
         <v>302</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C88" s="5">
         <v>5</v>
@@ -4220,7 +4247,7 @@
         <v>50</v>
       </c>
       <c r="I88" s="4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="J88" s="1"/>
       <c r="K88" s="1"/>
@@ -4232,7 +4259,7 @@
         <v>310</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C89" s="5">
         <v>2</v>
@@ -4253,7 +4280,7 @@
         <v>0</v>
       </c>
       <c r="I89" s="4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J89" s="1"/>
       <c r="K89" s="1"/>
@@ -4265,7 +4292,7 @@
         <v>311</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C90" s="5">
         <v>2</v>
@@ -4286,7 +4313,7 @@
         <v>0</v>
       </c>
       <c r="I90" s="4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J90" s="1"/>
       <c r="K90" s="1"/>
@@ -4298,7 +4325,7 @@
         <v>312</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C91" s="5">
         <v>2</v>
@@ -4319,7 +4346,7 @@
         <v>0</v>
       </c>
       <c r="I91" s="4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J91" s="1"/>
       <c r="K91" s="1"/>
@@ -4331,7 +4358,7 @@
         <v>320</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C92" s="5">
         <v>5</v>
@@ -4352,7 +4379,7 @@
         <v>1000</v>
       </c>
       <c r="I92" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="J92" s="1"/>
       <c r="K92" s="1"/>
@@ -4364,7 +4391,7 @@
         <v>321</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C93" s="5">
         <v>5</v>
@@ -4385,7 +4412,7 @@
         <v>1000</v>
       </c>
       <c r="I93" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="J93" s="1"/>
       <c r="K93" s="1"/>
@@ -4397,7 +4424,7 @@
         <v>322</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C94" s="5">
         <v>5</v>
@@ -4418,7 +4445,7 @@
         <v>1000</v>
       </c>
       <c r="I94" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="J94" s="1"/>
       <c r="K94" s="1"/>
@@ -4430,7 +4457,7 @@
         <v>330</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C95" s="5">
         <v>4</v>
@@ -4451,7 +4478,7 @@
         <v>6</v>
       </c>
       <c r="I95" s="4" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="J95" s="1"/>
       <c r="K95" s="1"/>
@@ -4463,7 +4490,7 @@
         <v>331</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C96" s="5">
         <v>4</v>
@@ -4484,7 +4511,7 @@
         <v>6</v>
       </c>
       <c r="I96" s="4" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="J96" s="1"/>
       <c r="K96" s="1"/>
@@ -4496,7 +4523,7 @@
         <v>332</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C97" s="5">
         <v>4</v>
@@ -4517,12 +4544,105 @@
         <v>6</v>
       </c>
       <c r="I97" s="4" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="J97" s="1"/>
       <c r="K97" s="1"/>
       <c r="L97" s="1"/>
       <c r="M97" s="1"/>
+    </row>
+    <row r="98" ht="84" spans="1:9">
+      <c r="A98">
+        <v>340</v>
+      </c>
+      <c r="B98" t="s">
+        <v>97</v>
+      </c>
+      <c r="C98">
+        <v>2</v>
+      </c>
+      <c r="D98">
+        <v>3</v>
+      </c>
+      <c r="E98">
+        <v>20</v>
+      </c>
+      <c r="F98">
+        <v>15</v>
+      </c>
+      <c r="G98">
+        <v>0</v>
+      </c>
+      <c r="H98">
+        <v>0</v>
+      </c>
+      <c r="I98" s="8" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="99" ht="84" spans="1:9">
+      <c r="A99">
+        <v>341</v>
+      </c>
+      <c r="B99" t="s">
+        <v>97</v>
+      </c>
+      <c r="C99">
+        <v>2</v>
+      </c>
+      <c r="D99">
+        <v>3</v>
+      </c>
+      <c r="E99">
+        <v>30</v>
+      </c>
+      <c r="F99">
+        <v>20</v>
+      </c>
+      <c r="G99">
+        <v>0</v>
+      </c>
+      <c r="H99">
+        <v>0</v>
+      </c>
+      <c r="I99" s="8" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="100" ht="84" spans="1:9">
+      <c r="A100">
+        <v>342</v>
+      </c>
+      <c r="B100" t="s">
+        <v>97</v>
+      </c>
+      <c r="C100">
+        <v>2</v>
+      </c>
+      <c r="D100">
+        <v>3</v>
+      </c>
+      <c r="E100">
+        <v>40</v>
+      </c>
+      <c r="F100">
+        <v>25</v>
+      </c>
+      <c r="G100">
+        <v>0</v>
+      </c>
+      <c r="H100">
+        <v>0</v>
+      </c>
+      <c r="I100" s="8" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="101" spans="9:9">
+      <c r="I101" s="8"/>
+    </row>
+    <row r="102" spans="9:9">
+      <c r="I102" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/ArtRes/Excel/灵居配置表.xlsx
+++ b/Assets/ArtRes/Excel/灵居配置表.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="114">
   <si>
     <t>id</t>
   </si>
@@ -76,6 +76,21 @@
     <t>missRate</t>
   </si>
   <si>
+    <t>atk_sound</t>
+  </si>
+  <si>
+    <t>atk_effect</t>
+  </si>
+  <si>
+    <t>redeployTime</t>
+  </si>
+  <si>
+    <t>passivesbuff</t>
+  </si>
+  <si>
+    <t>skill</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -134,6 +149,21 @@
   </si>
   <si>
     <t>闪避率（0-1）</t>
+  </si>
+  <si>
+    <t>攻击音效名</t>
+  </si>
+  <si>
+    <t>施加在目标上的特效</t>
+  </si>
+  <si>
+    <t>再部署时间</t>
+  </si>
+  <si>
+    <t>被动，会在角色初始添加一些buff，用,分隔</t>
+  </si>
+  <si>
+    <t>攻击</t>
   </si>
   <si>
     <t>工具箱</t>
@@ -143,16 +173,31 @@
 [装甲10]：受到的伤害减10</t>
   </si>
   <si>
+    <t>Sfx_Battle_Chequers_Chest_Attack</t>
+  </si>
+  <si>
+    <t>BlizzardPrison</t>
+  </si>
+  <si>
     <t>扳手</t>
   </si>
   <si>
     <t>[攻击]：恢复本行其它队友8点血量</t>
   </si>
   <si>
+    <t>Sfx_Battle_Chequers_Wrench_Attack</t>
+  </si>
+  <si>
     <t>棒球</t>
   </si>
   <si>
     <t>[亡语]：对本行最前方的敌人造成40点伤害</t>
+  </si>
+  <si>
+    <t>Sfx_Battle_Chequers_Baseball_Attack</t>
+  </si>
+  <si>
+    <t>hit_pj</t>
   </si>
   <si>
     <t>盒子</t>
@@ -1326,7 +1371,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O102"/>
+  <dimension ref="A1:T102"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="9" max="9" width="26.2727272727273" customWidth="1"/>
@@ -1334,9 +1379,14 @@
     <col min="12" max="12" width="12.7272727272727" customWidth="1"/>
     <col min="13" max="13" width="13.3636363636364" customWidth="1"/>
     <col min="14" max="14" width="11.2727272727273" customWidth="1"/>
+    <col min="15" max="15" width="12.7272727272727" customWidth="1"/>
+    <col min="16" max="16" width="35.4545454545455" customWidth="1"/>
+    <col min="17" max="17" width="15.2727272727273" customWidth="1"/>
+    <col min="18" max="18" width="12.5454545454545" customWidth="1"/>
+    <col min="19" max="19" width="12.8181818181818" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:20">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1382,57 +1432,87 @@
       <c r="O1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20">
       <c r="A2" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="N2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="O2" t="s">
-        <v>15</v>
+        <v>20</v>
+      </c>
+      <c r="P2" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>21</v>
+      </c>
+      <c r="R2" t="s">
+        <v>23</v>
+      </c>
+      <c r="S2" t="s">
+        <v>21</v>
+      </c>
+      <c r="T2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -1447,59 +1527,74 @@
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
-    <row r="4" ht="98" customHeight="1" spans="1:15">
+    <row r="4" ht="98" customHeight="1" spans="1:20">
       <c r="A4" s="1" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="N4" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="O4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" ht="42" spans="1:13">
+        <v>39</v>
+      </c>
+      <c r="P4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q4" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="R4" t="s">
+        <v>42</v>
+      </c>
+      <c r="S4" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="T4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" ht="42" spans="1:18">
       <c r="A5" s="1">
         <v>10</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="C5" s="1">
         <v>3</v>
@@ -1520,7 +1615,7 @@
         <v>20</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="J5" s="1"/>
       <c r="K5" s="1">
@@ -1528,13 +1623,22 @@
       </c>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
-    </row>
-    <row r="6" ht="42" spans="1:13">
+      <c r="P5" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>48</v>
+      </c>
+      <c r="R5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" ht="42" spans="1:18">
       <c r="A6" s="1">
         <v>11</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="C6" s="1">
         <v>3</v>
@@ -1555,7 +1659,7 @@
         <v>20</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="J6" s="1"/>
       <c r="K6" s="1">
@@ -1563,13 +1667,22 @@
       </c>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
-    </row>
-    <row r="7" ht="42" spans="1:13">
+      <c r="P6" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>48</v>
+      </c>
+      <c r="R6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" ht="42" spans="1:18">
       <c r="A7" s="1">
         <v>12</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="C7" s="1">
         <v>3</v>
@@ -1590,7 +1703,7 @@
         <v>20</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="J7" s="1"/>
       <c r="K7" s="1">
@@ -1598,13 +1711,22 @@
       </c>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
-    </row>
-    <row r="8" ht="28" spans="1:13">
+      <c r="P7" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>48</v>
+      </c>
+      <c r="R7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" ht="28" spans="1:18">
       <c r="A8" s="1">
         <v>20</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="C8" s="1">
         <v>2</v>
@@ -1625,7 +1747,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="J8" s="1">
         <v>3</v>
@@ -1635,13 +1757,22 @@
       </c>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
-    </row>
-    <row r="9" ht="28" spans="1:13">
+      <c r="P8" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>48</v>
+      </c>
+      <c r="R8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" ht="28" spans="1:18">
       <c r="A9" s="1">
         <v>21</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="C9" s="1">
         <v>2</v>
@@ -1662,7 +1793,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="J9" s="1">
         <v>3</v>
@@ -1672,13 +1803,22 @@
       </c>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
-    </row>
-    <row r="10" ht="28" spans="1:13">
+      <c r="P9" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>48</v>
+      </c>
+      <c r="R9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" ht="28" spans="1:18">
       <c r="A10" s="1">
         <v>22</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="C10" s="1">
         <v>2</v>
@@ -1699,7 +1839,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="J10" s="1">
         <v>3</v>
@@ -1709,13 +1849,22 @@
       </c>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
-    </row>
-    <row r="11" ht="28" spans="1:13">
+      <c r="P10" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>48</v>
+      </c>
+      <c r="R10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" ht="28" spans="1:18">
       <c r="A11" s="1">
         <v>30</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="C11" s="1">
         <v>1</v>
@@ -1736,7 +1885,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="J11" s="1"/>
       <c r="K11" s="1">
@@ -1744,13 +1893,22 @@
       </c>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
-    </row>
-    <row r="12" ht="28" spans="1:13">
+      <c r="P11" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>55</v>
+      </c>
+      <c r="R11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" ht="28" spans="1:18">
       <c r="A12" s="1">
         <v>31</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="C12" s="1">
         <v>1</v>
@@ -1771,7 +1929,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="J12" s="1"/>
       <c r="K12" s="1">
@@ -1779,13 +1937,22 @@
       </c>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
-    </row>
-    <row r="13" ht="28" spans="1:13">
+      <c r="P12" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>55</v>
+      </c>
+      <c r="R12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" ht="28" spans="1:18">
       <c r="A13" s="1">
         <v>32</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="C13" s="1">
         <v>1</v>
@@ -1806,7 +1973,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="J13" s="1"/>
       <c r="K13" s="1">
@@ -1814,13 +1981,22 @@
       </c>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
-    </row>
-    <row r="14" ht="28" spans="1:13">
+      <c r="P13" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>55</v>
+      </c>
+      <c r="R13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" ht="28" spans="1:18">
       <c r="A14" s="1">
         <v>40</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="C14" s="1">
         <v>2</v>
@@ -1837,7 +2013,7 @@
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
       <c r="I14" s="4" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="J14" s="1"/>
       <c r="K14" s="1">
@@ -1845,13 +2021,19 @@
       </c>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
-    </row>
-    <row r="15" ht="28" spans="1:13">
+      <c r="Q14" t="s">
+        <v>55</v>
+      </c>
+      <c r="R14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" ht="28" spans="1:18">
       <c r="A15" s="1">
         <v>41</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="C15" s="1">
         <v>2</v>
@@ -1868,7 +2050,7 @@
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
       <c r="I15" s="4" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="J15" s="1"/>
       <c r="K15" s="1">
@@ -1876,13 +2058,19 @@
       </c>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
-    </row>
-    <row r="16" ht="28" spans="1:13">
+      <c r="Q15" t="s">
+        <v>55</v>
+      </c>
+      <c r="R15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" ht="28" spans="1:18">
       <c r="A16" s="1">
         <v>42</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="C16" s="1">
         <v>2</v>
@@ -1899,7 +2087,7 @@
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="4" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="J16" s="1"/>
       <c r="K16" s="1">
@@ -1907,13 +2095,19 @@
       </c>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
-    </row>
-    <row r="17" ht="42" spans="1:13">
+      <c r="Q16" t="s">
+        <v>55</v>
+      </c>
+      <c r="R16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" ht="42" spans="1:18">
       <c r="A17" s="1">
         <v>50</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="C17" s="1">
         <v>4</v>
@@ -1930,7 +2124,7 @@
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
       <c r="I17" s="4" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="J17" s="1"/>
       <c r="K17" s="1">
@@ -1938,13 +2132,16 @@
       </c>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
-    </row>
-    <row r="18" ht="42" spans="1:13">
+      <c r="R17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" ht="42" spans="1:18">
       <c r="A18" s="1">
         <v>51</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="C18" s="1">
         <v>4</v>
@@ -1961,7 +2158,7 @@
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
       <c r="I18" s="4" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="J18" s="1"/>
       <c r="K18" s="1">
@@ -1969,13 +2166,16 @@
       </c>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
-    </row>
-    <row r="19" ht="42" spans="1:13">
+      <c r="R18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" ht="42" spans="1:18">
       <c r="A19" s="1">
         <v>52</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="C19" s="1">
         <v>4</v>
@@ -1992,7 +2192,7 @@
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
       <c r="I19" s="4" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="J19" s="1"/>
       <c r="K19" s="1">
@@ -2000,13 +2200,16 @@
       </c>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
-    </row>
-    <row r="20" ht="28" spans="1:13">
+      <c r="R19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" ht="28" spans="1:18">
       <c r="A20" s="1">
         <v>60</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="C20" s="4">
         <v>3</v>
@@ -2027,7 +2230,7 @@
         <v>0</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="J20" s="1"/>
       <c r="K20" s="1">
@@ -2035,13 +2238,16 @@
       </c>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
-    </row>
-    <row r="21" ht="28" spans="1:13">
+      <c r="R20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" ht="28" spans="1:18">
       <c r="A21" s="1">
         <v>61</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="C21" s="1">
         <v>3</v>
@@ -2062,7 +2268,7 @@
         <v>0</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="J21" s="1"/>
       <c r="K21" s="1">
@@ -2070,13 +2276,16 @@
       </c>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
-    </row>
-    <row r="22" ht="28" spans="1:13">
+      <c r="R21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" ht="28" spans="1:18">
       <c r="A22" s="1">
         <v>62</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="C22" s="1">
         <v>3</v>
@@ -2097,7 +2306,7 @@
         <v>0</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="J22" s="1"/>
       <c r="K22" s="1">
@@ -2105,13 +2314,16 @@
       </c>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
-    </row>
-    <row r="23" ht="28" spans="1:13">
+      <c r="R22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" ht="28" spans="1:18">
       <c r="A23" s="1">
         <v>70</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="C23" s="1">
         <v>5</v>
@@ -2132,7 +2344,7 @@
         <v>0</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="J23" s="1"/>
       <c r="K23" s="1">
@@ -2140,13 +2352,16 @@
       </c>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
-    </row>
-    <row r="24" ht="28" spans="1:13">
+      <c r="R23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" ht="28" spans="1:18">
       <c r="A24" s="1">
         <v>71</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="C24" s="1">
         <v>5</v>
@@ -2167,7 +2382,7 @@
         <v>0</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="J24" s="1"/>
       <c r="K24" s="1">
@@ -2175,13 +2390,16 @@
       </c>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
-    </row>
-    <row r="25" ht="28" spans="1:13">
+      <c r="R24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" ht="28" spans="1:18">
       <c r="A25" s="1">
         <v>72</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="C25" s="1">
         <v>5</v>
@@ -2202,7 +2420,7 @@
         <v>0</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="J25" s="1"/>
       <c r="K25" s="1">
@@ -2210,13 +2428,16 @@
       </c>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
-    </row>
-    <row r="26" spans="1:13">
+      <c r="R25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18">
       <c r="A26" s="1">
         <v>80</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="C26" s="1">
         <v>1</v>
@@ -2237,7 +2458,7 @@
         <v>0</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="J26" s="1"/>
       <c r="K26" s="1">
@@ -2245,13 +2466,16 @@
       </c>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
-    </row>
-    <row r="27" spans="1:13">
+      <c r="R26">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18">
       <c r="A27" s="1">
         <v>81</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="C27" s="1">
         <v>1</v>
@@ -2272,7 +2496,7 @@
         <v>0</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="J27" s="1"/>
       <c r="K27" s="1">
@@ -2280,13 +2504,16 @@
       </c>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
-    </row>
-    <row r="28" spans="1:13">
+      <c r="R27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18">
       <c r="A28" s="1">
         <v>82</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="C28" s="1">
         <v>1</v>
@@ -2307,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="J28" s="1"/>
       <c r="K28" s="1">
@@ -2315,13 +2542,16 @@
       </c>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
-    </row>
-    <row r="29" spans="1:13">
+      <c r="R28">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18">
       <c r="A29" s="1">
         <v>90</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="C29" s="1">
         <v>1</v>
@@ -2348,13 +2578,16 @@
       </c>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
-    </row>
-    <row r="30" spans="1:13">
+      <c r="R29">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18">
       <c r="A30" s="1">
         <v>91</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="C30" s="1">
         <v>1</v>
@@ -2381,13 +2614,16 @@
       </c>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
-    </row>
-    <row r="31" spans="1:13">
+      <c r="R30">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18">
       <c r="A31" s="1">
         <v>92</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="C31" s="1">
         <v>1</v>
@@ -2414,13 +2650,16 @@
       </c>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
-    </row>
-    <row r="32" spans="1:13">
+      <c r="R31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18">
       <c r="A32" s="1">
         <v>100</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
@@ -2435,13 +2674,16 @@
       </c>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
-    </row>
-    <row r="33" spans="1:13">
+      <c r="R32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18">
       <c r="A33" s="1">
         <v>101</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
@@ -2456,13 +2698,16 @@
       </c>
       <c r="L33" s="1"/>
       <c r="M33" s="1"/>
-    </row>
-    <row r="34" spans="1:13">
+      <c r="R33">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18">
       <c r="A34" s="1">
         <v>102</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
@@ -2477,13 +2722,16 @@
       </c>
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
-    </row>
-    <row r="35" ht="28" spans="1:13">
+      <c r="R34">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" ht="28" spans="1:18">
       <c r="A35" s="1">
         <v>110</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="C35" s="5">
         <v>1</v>
@@ -2504,7 +2752,7 @@
         <v>0</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="J35" s="1"/>
       <c r="K35" s="1">
@@ -2512,13 +2760,16 @@
       </c>
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
-    </row>
-    <row r="36" ht="28" spans="1:13">
+      <c r="R35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" ht="28" spans="1:18">
       <c r="A36" s="1">
         <v>120</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="C36" s="5">
         <v>1</v>
@@ -2539,7 +2790,7 @@
         <v>0</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="J36" s="1"/>
       <c r="K36" s="1">
@@ -2547,13 +2798,16 @@
       </c>
       <c r="L36" s="1"/>
       <c r="M36" s="1"/>
-    </row>
-    <row r="37" ht="28" spans="1:13">
+      <c r="R36">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" ht="28" spans="1:18">
       <c r="A37" s="1">
         <v>130</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="C37" s="5">
         <v>1</v>
@@ -2574,7 +2828,7 @@
         <v>0</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="J37" s="1"/>
       <c r="K37" s="1">
@@ -2582,13 +2836,16 @@
       </c>
       <c r="L37" s="1"/>
       <c r="M37" s="1"/>
-    </row>
-    <row r="38" ht="42" spans="1:13">
+      <c r="R37">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" ht="42" spans="1:18">
       <c r="A38" s="1">
         <v>140</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="C38" s="6">
         <v>2</v>
@@ -2609,19 +2866,22 @@
         <v>0</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
       <c r="L38" s="1"/>
       <c r="M38" s="1"/>
-    </row>
-    <row r="39" ht="42" spans="1:13">
+      <c r="R38">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" ht="42" spans="1:18">
       <c r="A39" s="1">
         <v>141</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="C39" s="6">
         <v>2</v>
@@ -2642,19 +2902,22 @@
         <v>0</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
-    </row>
-    <row r="40" ht="42" spans="1:13">
+      <c r="R39">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" ht="42" spans="1:18">
       <c r="A40" s="1">
         <v>142</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="C40" s="6">
         <v>2</v>
@@ -2675,19 +2938,22 @@
         <v>0</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
       <c r="L40" s="1"/>
       <c r="M40" s="1"/>
-    </row>
-    <row r="41" spans="1:13">
+      <c r="R40">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18">
       <c r="A41" s="1">
         <v>150</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="C41" s="5">
         <v>3</v>
@@ -2708,19 +2974,22 @@
         <v>50</v>
       </c>
       <c r="I41" s="5" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="J41" s="1"/>
       <c r="K41" s="1"/>
       <c r="L41" s="1"/>
       <c r="M41" s="1"/>
-    </row>
-    <row r="42" spans="1:13">
+      <c r="R41">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18">
       <c r="A42" s="1">
         <v>151</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="C42" s="5">
         <v>3</v>
@@ -2741,19 +3010,22 @@
         <v>50</v>
       </c>
       <c r="I42" s="5" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
       <c r="L42" s="1"/>
       <c r="M42" s="1"/>
-    </row>
-    <row r="43" spans="1:13">
+      <c r="R42">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18">
       <c r="A43" s="1">
         <v>152</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="C43" s="5">
         <v>3</v>
@@ -2774,19 +3046,22 @@
         <v>50</v>
       </c>
       <c r="I43" s="5" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="J43" s="1"/>
       <c r="K43" s="1"/>
       <c r="L43" s="1"/>
       <c r="M43" s="1"/>
-    </row>
-    <row r="44" spans="1:13">
+      <c r="R43">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18">
       <c r="A44" s="1">
         <v>160</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="C44" s="4">
         <v>1</v>
@@ -2811,13 +3086,16 @@
       <c r="K44" s="1"/>
       <c r="L44" s="1"/>
       <c r="M44" s="1"/>
-    </row>
-    <row r="45" spans="1:13">
+      <c r="R44">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18">
       <c r="A45" s="1">
         <v>161</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="C45" s="4">
         <v>1</v>
@@ -2842,13 +3120,16 @@
       <c r="K45" s="1"/>
       <c r="L45" s="1"/>
       <c r="M45" s="1"/>
-    </row>
-    <row r="46" spans="1:13">
+      <c r="R45">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18">
       <c r="A46" s="1">
         <v>162</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="C46" s="4">
         <v>1</v>
@@ -2873,13 +3154,16 @@
       <c r="K46" s="1"/>
       <c r="L46" s="1"/>
       <c r="M46" s="1"/>
-    </row>
-    <row r="47" spans="1:13">
+      <c r="R46">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18">
       <c r="A47" s="1">
         <v>170</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="C47" s="5">
         <v>1</v>
@@ -2904,13 +3188,16 @@
       <c r="K47" s="1"/>
       <c r="L47" s="1"/>
       <c r="M47" s="1"/>
-    </row>
-    <row r="48" spans="1:13">
+      <c r="R47">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18">
       <c r="A48" s="1">
         <v>171</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="C48" s="5">
         <v>1</v>
@@ -2935,13 +3222,16 @@
       <c r="K48" s="1"/>
       <c r="L48" s="1"/>
       <c r="M48" s="1"/>
-    </row>
-    <row r="49" spans="1:13">
+      <c r="R48">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18">
       <c r="A49" s="1">
         <v>172</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="C49" s="5">
         <v>1</v>
@@ -2966,13 +3256,16 @@
       <c r="K49" s="1"/>
       <c r="L49" s="1"/>
       <c r="M49" s="1"/>
-    </row>
-    <row r="50" ht="28" spans="1:13">
+      <c r="R49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" ht="28" spans="1:18">
       <c r="A50" s="1">
         <v>180</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="C50" s="5">
         <v>2</v>
@@ -2993,19 +3286,22 @@
         <v>0</v>
       </c>
       <c r="I50" s="4" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="J50" s="1"/>
       <c r="K50" s="1"/>
       <c r="L50" s="1"/>
       <c r="M50" s="1"/>
-    </row>
-    <row r="51" ht="28" spans="1:13">
+      <c r="R50">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" ht="28" spans="1:18">
       <c r="A51" s="1">
         <v>181</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="C51" s="5">
         <v>2</v>
@@ -3026,19 +3322,22 @@
         <v>0</v>
       </c>
       <c r="I51" s="4" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="J51" s="1"/>
       <c r="K51" s="1"/>
       <c r="L51" s="1"/>
       <c r="M51" s="1"/>
-    </row>
-    <row r="52" ht="28" spans="1:13">
+      <c r="R51">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" ht="28" spans="1:18">
       <c r="A52" s="1">
         <v>182</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="C52" s="5">
         <v>2</v>
@@ -3059,19 +3358,22 @@
         <v>0</v>
       </c>
       <c r="I52" s="4" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
       <c r="L52" s="1"/>
       <c r="M52" s="1"/>
-    </row>
-    <row r="53" spans="1:13">
+      <c r="R52">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18">
       <c r="A53" s="1">
         <v>190</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="C53" s="5">
         <v>4</v>
@@ -3092,19 +3394,22 @@
         <v>0</v>
       </c>
       <c r="I53" s="5" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="J53" s="1"/>
       <c r="K53" s="1"/>
       <c r="L53" s="1"/>
       <c r="M53" s="1"/>
-    </row>
-    <row r="54" spans="1:13">
+      <c r="R53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18">
       <c r="A54" s="1">
         <v>191</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="C54" s="5">
         <v>4</v>
@@ -3125,19 +3430,22 @@
         <v>0</v>
       </c>
       <c r="I54" s="5" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="J54" s="1"/>
       <c r="K54" s="1"/>
       <c r="L54" s="1"/>
       <c r="M54" s="1"/>
-    </row>
-    <row r="55" spans="1:13">
+      <c r="R54">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18">
       <c r="A55" s="1">
         <v>192</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="C55" s="5">
         <v>4</v>
@@ -3158,19 +3466,22 @@
         <v>0</v>
       </c>
       <c r="I55" s="5" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="J55" s="1"/>
       <c r="K55" s="1"/>
       <c r="L55" s="1"/>
       <c r="M55" s="1"/>
-    </row>
-    <row r="56" ht="42" spans="1:13">
+      <c r="R55">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" ht="42" spans="1:18">
       <c r="A56" s="1">
         <v>200</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="C56" s="4">
         <v>4</v>
@@ -3191,19 +3502,22 @@
         <v>0</v>
       </c>
       <c r="I56" s="4" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="J56" s="1"/>
       <c r="K56" s="1"/>
       <c r="L56" s="1"/>
       <c r="M56" s="1"/>
-    </row>
-    <row r="57" ht="42" spans="1:13">
+      <c r="R56">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" ht="42" spans="1:18">
       <c r="A57" s="1">
         <v>201</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="C57" s="4">
         <v>4</v>
@@ -3224,19 +3538,22 @@
         <v>0</v>
       </c>
       <c r="I57" s="4" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="J57" s="1"/>
       <c r="K57" s="1"/>
       <c r="L57" s="1"/>
       <c r="M57" s="1"/>
-    </row>
-    <row r="58" ht="42" spans="1:13">
+      <c r="R57">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" ht="42" spans="1:18">
       <c r="A58" s="1">
         <v>202</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="C58" s="4">
         <v>4</v>
@@ -3257,19 +3574,22 @@
         <v>0</v>
       </c>
       <c r="I58" s="4" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="J58" s="1"/>
       <c r="K58" s="1"/>
       <c r="L58" s="1"/>
       <c r="M58" s="1"/>
-    </row>
-    <row r="59" ht="70" spans="1:13">
+      <c r="R58">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" ht="70" spans="1:18">
       <c r="A59" s="1">
         <v>210</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="C59" s="5">
         <v>5</v>
@@ -3290,19 +3610,22 @@
         <v>50</v>
       </c>
       <c r="I59" s="4" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="J59" s="1"/>
       <c r="K59" s="1"/>
       <c r="L59" s="1"/>
       <c r="M59" s="1"/>
-    </row>
-    <row r="60" ht="68" customHeight="1" spans="1:13">
+      <c r="R59">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" ht="68" customHeight="1" spans="1:18">
       <c r="A60" s="1">
         <v>211</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="C60" s="5">
         <v>5</v>
@@ -3323,19 +3646,22 @@
         <v>50</v>
       </c>
       <c r="I60" s="4" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="J60" s="1"/>
       <c r="K60" s="1"/>
       <c r="L60" s="1"/>
       <c r="M60" s="1"/>
-    </row>
-    <row r="61" ht="70" spans="1:13">
+      <c r="R60">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" ht="70" spans="1:18">
       <c r="A61" s="1">
         <v>212</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="C61" s="5">
         <v>5</v>
@@ -3356,19 +3682,22 @@
         <v>50</v>
       </c>
       <c r="I61" s="4" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="J61" s="1"/>
       <c r="K61" s="1"/>
       <c r="L61" s="1"/>
       <c r="M61" s="1"/>
-    </row>
-    <row r="62" ht="28" spans="1:13">
+      <c r="R61">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" ht="28" spans="1:18">
       <c r="A62" s="1">
         <v>220</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="C62" s="5">
         <v>1</v>
@@ -3389,19 +3718,22 @@
         <v>0</v>
       </c>
       <c r="I62" s="4" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="J62" s="1"/>
       <c r="K62" s="1"/>
       <c r="L62" s="1"/>
       <c r="M62" s="1"/>
-    </row>
-    <row r="63" ht="28" spans="1:13">
+      <c r="R62">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" ht="28" spans="1:18">
       <c r="A63" s="1">
         <v>221</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="C63" s="5">
         <v>1</v>
@@ -3422,19 +3754,22 @@
         <v>0</v>
       </c>
       <c r="I63" s="4" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="J63" s="1"/>
       <c r="K63" s="1"/>
       <c r="L63" s="1"/>
       <c r="M63" s="1"/>
-    </row>
-    <row r="64" ht="28" spans="1:13">
+      <c r="R63">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" ht="28" spans="1:18">
       <c r="A64" s="1">
         <v>222</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="C64" s="5">
         <v>1</v>
@@ -3455,19 +3790,22 @@
         <v>0</v>
       </c>
       <c r="I64" s="4" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="J64" s="1"/>
       <c r="K64" s="1"/>
       <c r="L64" s="1"/>
       <c r="M64" s="1"/>
-    </row>
-    <row r="65" ht="42" spans="1:13">
+      <c r="R64">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" ht="42" spans="1:18">
       <c r="A65" s="1">
         <v>230</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="C65" s="5">
         <v>3</v>
@@ -3488,19 +3826,22 @@
         <v>10</v>
       </c>
       <c r="I65" s="4" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="J65" s="1"/>
       <c r="K65" s="1"/>
       <c r="L65" s="1"/>
       <c r="M65" s="1"/>
-    </row>
-    <row r="66" ht="42" spans="1:13">
+      <c r="R65">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66" ht="42" spans="1:18">
       <c r="A66" s="1">
         <v>231</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="C66" s="5">
         <v>3</v>
@@ -3521,19 +3862,22 @@
         <v>10</v>
       </c>
       <c r="I66" s="4" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="J66" s="1"/>
       <c r="K66" s="1"/>
       <c r="L66" s="1"/>
       <c r="M66" s="1"/>
-    </row>
-    <row r="67" ht="42" spans="1:13">
+      <c r="R66">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" ht="42" spans="1:18">
       <c r="A67" s="1">
         <v>232</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="C67" s="5">
         <v>3</v>
@@ -3554,19 +3898,22 @@
         <v>10</v>
       </c>
       <c r="I67" s="4" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="J67" s="1"/>
       <c r="K67" s="1"/>
       <c r="L67" s="1"/>
       <c r="M67" s="1"/>
-    </row>
-    <row r="68" ht="42" spans="1:13">
+      <c r="R67">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68" ht="42" spans="1:18">
       <c r="A68" s="1">
         <v>240</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="C68" s="5">
         <v>2</v>
@@ -3587,19 +3934,22 @@
         <v>0</v>
       </c>
       <c r="I68" s="4" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="J68" s="1"/>
       <c r="K68" s="1"/>
       <c r="L68" s="1"/>
       <c r="M68" s="1"/>
-    </row>
-    <row r="69" ht="42" spans="1:13">
+      <c r="R68">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69" ht="42" spans="1:18">
       <c r="A69" s="1">
         <v>241</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="C69" s="5">
         <v>2</v>
@@ -3620,19 +3970,22 @@
         <v>0</v>
       </c>
       <c r="I69" s="4" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="J69" s="1"/>
       <c r="K69" s="1"/>
       <c r="L69" s="1"/>
       <c r="M69" s="1"/>
-    </row>
-    <row r="70" ht="42" spans="1:13">
+      <c r="R69">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" ht="42" spans="1:18">
       <c r="A70" s="1">
         <v>242</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="C70" s="5">
         <v>2</v>
@@ -3653,19 +4006,22 @@
         <v>0</v>
       </c>
       <c r="I70" s="4" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="J70" s="1"/>
       <c r="K70" s="1"/>
       <c r="L70" s="1"/>
       <c r="M70" s="1"/>
-    </row>
-    <row r="71" spans="1:13">
+      <c r="R70">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:18">
       <c r="A71" s="1">
         <v>250</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="C71" s="4">
         <v>3</v>
@@ -3686,19 +4042,22 @@
         <v>20</v>
       </c>
       <c r="I71" s="4" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="J71" s="1"/>
       <c r="K71" s="1"/>
       <c r="L71" s="1"/>
       <c r="M71" s="1"/>
-    </row>
-    <row r="72" spans="1:13">
+      <c r="R71">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:18">
       <c r="A72" s="1">
         <v>251</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="C72" s="4">
         <v>3</v>
@@ -3719,19 +4078,22 @@
         <v>20</v>
       </c>
       <c r="I72" s="4" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="J72" s="1"/>
       <c r="K72" s="1"/>
       <c r="L72" s="1"/>
       <c r="M72" s="1"/>
-    </row>
-    <row r="73" spans="1:13">
+      <c r="R72">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:18">
       <c r="A73" s="1">
         <v>252</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="C73" s="4">
         <v>3</v>
@@ -3752,19 +4114,22 @@
         <v>20</v>
       </c>
       <c r="I73" s="4" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="J73" s="1"/>
       <c r="K73" s="1"/>
       <c r="L73" s="1"/>
       <c r="M73" s="1"/>
-    </row>
-    <row r="74" ht="70" spans="1:13">
+      <c r="R73">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74" ht="70" spans="1:18">
       <c r="A74" s="1">
         <v>260</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="C74" s="4">
         <v>1</v>
@@ -3785,19 +4150,22 @@
         <v>0</v>
       </c>
       <c r="I74" s="4" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="J74" s="1"/>
       <c r="K74" s="1"/>
       <c r="L74" s="1"/>
       <c r="M74" s="1"/>
-    </row>
-    <row r="75" ht="70" spans="1:13">
+      <c r="R74">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="75" ht="70" spans="1:18">
       <c r="A75" s="1">
         <v>261</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="C75" s="4">
         <v>1</v>
@@ -3818,19 +4186,22 @@
         <v>0</v>
       </c>
       <c r="I75" s="4" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="J75" s="1"/>
       <c r="K75" s="1"/>
       <c r="L75" s="1"/>
       <c r="M75" s="1"/>
-    </row>
-    <row r="76" ht="70" spans="1:13">
+      <c r="R75">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76" ht="70" spans="1:18">
       <c r="A76" s="1">
         <v>262</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="C76" s="4">
         <v>1</v>
@@ -3851,19 +4222,22 @@
         <v>0</v>
       </c>
       <c r="I76" s="4" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="J76" s="1"/>
       <c r="K76" s="1"/>
       <c r="L76" s="1"/>
       <c r="M76" s="1"/>
-    </row>
-    <row r="77" ht="70" spans="1:13">
+      <c r="R76">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77" ht="70" spans="1:18">
       <c r="A77" s="1">
         <v>270</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="C77" s="4">
         <v>2</v>
@@ -3884,19 +4258,22 @@
         <v>0</v>
       </c>
       <c r="I77" s="4" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="J77" s="1"/>
       <c r="K77" s="1"/>
       <c r="L77" s="1"/>
       <c r="M77" s="1"/>
-    </row>
-    <row r="78" ht="70" spans="1:13">
+      <c r="R77">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78" ht="70" spans="1:18">
       <c r="A78" s="1">
         <v>271</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="C78" s="4">
         <v>2</v>
@@ -3917,19 +4294,22 @@
         <v>0</v>
       </c>
       <c r="I78" s="4" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="J78" s="1"/>
       <c r="K78" s="1"/>
       <c r="L78" s="1"/>
       <c r="M78" s="1"/>
-    </row>
-    <row r="79" ht="70" spans="1:13">
+      <c r="R78">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79" ht="70" spans="1:18">
       <c r="A79" s="1">
         <v>272</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="C79" s="4">
         <v>2</v>
@@ -3950,19 +4330,22 @@
         <v>0</v>
       </c>
       <c r="I79" s="4" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="J79" s="1"/>
       <c r="K79" s="1"/>
       <c r="L79" s="1"/>
       <c r="M79" s="1"/>
-    </row>
-    <row r="80" ht="70" spans="1:13">
+      <c r="R79">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80" ht="70" spans="1:18">
       <c r="A80" s="1">
         <v>280</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="C80" s="4">
         <v>2</v>
@@ -3983,19 +4366,22 @@
         <v>0</v>
       </c>
       <c r="I80" s="4" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="J80" s="1"/>
       <c r="K80" s="1"/>
       <c r="L80" s="1"/>
       <c r="M80" s="1"/>
-    </row>
-    <row r="81" ht="70" spans="1:13">
+      <c r="R80">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="81" ht="70" spans="1:18">
       <c r="A81" s="1">
         <v>281</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="C81" s="4">
         <v>2</v>
@@ -4016,19 +4402,22 @@
         <v>0</v>
       </c>
       <c r="I81" s="4" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="J81" s="1"/>
       <c r="K81" s="1"/>
       <c r="L81" s="1"/>
       <c r="M81" s="1"/>
-    </row>
-    <row r="82" ht="70" spans="1:13">
+      <c r="R81">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="82" ht="70" spans="1:18">
       <c r="A82" s="1">
         <v>282</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="C82" s="4">
         <v>2</v>
@@ -4049,19 +4438,22 @@
         <v>0</v>
       </c>
       <c r="I82" s="4" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="J82" s="1"/>
       <c r="K82" s="1"/>
       <c r="L82" s="1"/>
       <c r="M82" s="1"/>
-    </row>
-    <row r="83" ht="84" spans="1:13">
+      <c r="R82">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83" ht="84" spans="1:18">
       <c r="A83" s="1">
         <v>290</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="C83" s="4">
         <v>3</v>
@@ -4082,19 +4474,22 @@
         <v>0</v>
       </c>
       <c r="I83" s="4" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="J83" s="1"/>
       <c r="K83" s="1"/>
       <c r="L83" s="1"/>
       <c r="M83" s="1"/>
-    </row>
-    <row r="84" ht="84" spans="1:13">
+      <c r="R83">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="84" ht="84" spans="1:18">
       <c r="A84" s="1">
         <v>291</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="C84" s="4">
         <v>3</v>
@@ -4115,19 +4510,22 @@
         <v>0</v>
       </c>
       <c r="I84" s="4" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="J84" s="1"/>
       <c r="K84" s="1"/>
       <c r="L84" s="1"/>
       <c r="M84" s="1"/>
-    </row>
-    <row r="85" ht="84" spans="1:13">
+      <c r="R84">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="85" ht="84" spans="1:18">
       <c r="A85" s="1">
         <v>292</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="C85" s="4">
         <v>3</v>
@@ -4148,19 +4546,22 @@
         <v>0</v>
       </c>
       <c r="I85" s="4" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="J85" s="1"/>
       <c r="K85" s="1"/>
       <c r="L85" s="1"/>
       <c r="M85" s="1"/>
-    </row>
-    <row r="86" ht="28" spans="1:13">
+      <c r="R85">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="86" ht="28" spans="1:18">
       <c r="A86" s="1">
         <v>300</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="C86" s="5">
         <v>5</v>
@@ -4181,19 +4582,22 @@
         <v>50</v>
       </c>
       <c r="I86" s="4" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="J86" s="1"/>
       <c r="K86" s="1"/>
       <c r="L86" s="1"/>
       <c r="M86" s="1"/>
-    </row>
-    <row r="87" ht="28" spans="1:13">
+      <c r="R86">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="87" ht="28" spans="1:18">
       <c r="A87" s="1">
         <v>301</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="C87" s="5">
         <v>5</v>
@@ -4214,19 +4618,22 @@
         <v>50</v>
       </c>
       <c r="I87" s="4" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="J87" s="1"/>
       <c r="K87" s="1"/>
       <c r="L87" s="1"/>
       <c r="M87" s="1"/>
-    </row>
-    <row r="88" ht="28" spans="1:13">
+      <c r="R87">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="88" ht="28" spans="1:18">
       <c r="A88" s="1">
         <v>302</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="C88" s="5">
         <v>5</v>
@@ -4247,19 +4654,22 @@
         <v>50</v>
       </c>
       <c r="I88" s="4" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="J88" s="1"/>
       <c r="K88" s="1"/>
       <c r="L88" s="1"/>
       <c r="M88" s="1"/>
-    </row>
-    <row r="89" ht="56" spans="1:13">
+      <c r="R88">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="89" ht="56" spans="1:18">
       <c r="A89" s="1">
         <v>310</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="C89" s="5">
         <v>2</v>
@@ -4280,19 +4690,22 @@
         <v>0</v>
       </c>
       <c r="I89" s="4" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="J89" s="1"/>
       <c r="K89" s="1"/>
       <c r="L89" s="1"/>
       <c r="M89" s="1"/>
-    </row>
-    <row r="90" ht="56" spans="1:13">
+      <c r="R89">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="90" ht="56" spans="1:18">
       <c r="A90" s="1">
         <v>311</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="C90" s="5">
         <v>2</v>
@@ -4313,19 +4726,22 @@
         <v>0</v>
       </c>
       <c r="I90" s="4" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="J90" s="1"/>
       <c r="K90" s="1"/>
       <c r="L90" s="1"/>
       <c r="M90" s="1"/>
-    </row>
-    <row r="91" ht="56" spans="1:13">
+      <c r="R90">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="91" ht="56" spans="1:18">
       <c r="A91" s="1">
         <v>312</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="C91" s="5">
         <v>2</v>
@@ -4346,19 +4762,22 @@
         <v>0</v>
       </c>
       <c r="I91" s="4" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="J91" s="1"/>
       <c r="K91" s="1"/>
       <c r="L91" s="1"/>
       <c r="M91" s="1"/>
-    </row>
-    <row r="92" ht="56" spans="1:13">
+      <c r="R91">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="92" ht="56" spans="1:18">
       <c r="A92" s="1">
         <v>320</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="C92" s="5">
         <v>5</v>
@@ -4379,19 +4798,22 @@
         <v>1000</v>
       </c>
       <c r="I92" s="4" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="J92" s="1"/>
       <c r="K92" s="1"/>
       <c r="L92" s="1"/>
       <c r="M92" s="1"/>
-    </row>
-    <row r="93" ht="56" spans="1:13">
+      <c r="R92">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93" ht="56" spans="1:18">
       <c r="A93" s="1">
         <v>321</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="C93" s="5">
         <v>5</v>
@@ -4412,19 +4834,22 @@
         <v>1000</v>
       </c>
       <c r="I93" s="4" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="J93" s="1"/>
       <c r="K93" s="1"/>
       <c r="L93" s="1"/>
       <c r="M93" s="1"/>
-    </row>
-    <row r="94" ht="56" spans="1:13">
+      <c r="R93">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94" ht="56" spans="1:18">
       <c r="A94" s="1">
         <v>322</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="C94" s="5">
         <v>5</v>
@@ -4445,19 +4870,22 @@
         <v>1000</v>
       </c>
       <c r="I94" s="4" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="J94" s="1"/>
       <c r="K94" s="1"/>
       <c r="L94" s="1"/>
       <c r="M94" s="1"/>
-    </row>
-    <row r="95" ht="28" spans="1:13">
+      <c r="R94">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95" ht="28" spans="1:18">
       <c r="A95" s="1">
         <v>330</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="C95" s="5">
         <v>4</v>
@@ -4478,19 +4906,22 @@
         <v>6</v>
       </c>
       <c r="I95" s="4" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="J95" s="1"/>
       <c r="K95" s="1"/>
       <c r="L95" s="1"/>
       <c r="M95" s="1"/>
-    </row>
-    <row r="96" ht="28" spans="1:13">
+      <c r="R95">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="96" ht="28" spans="1:18">
       <c r="A96" s="1">
         <v>331</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="C96" s="5">
         <v>4</v>
@@ -4511,19 +4942,22 @@
         <v>6</v>
       </c>
       <c r="I96" s="4" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="J96" s="1"/>
       <c r="K96" s="1"/>
       <c r="L96" s="1"/>
       <c r="M96" s="1"/>
-    </row>
-    <row r="97" ht="28" spans="1:13">
+      <c r="R96">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="97" ht="28" spans="1:18">
       <c r="A97" s="1">
         <v>332</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="C97" s="5">
         <v>4</v>
@@ -4544,19 +4978,22 @@
         <v>6</v>
       </c>
       <c r="I97" s="4" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="J97" s="1"/>
       <c r="K97" s="1"/>
       <c r="L97" s="1"/>
       <c r="M97" s="1"/>
-    </row>
-    <row r="98" ht="84" spans="1:9">
+      <c r="R97">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="98" ht="84" spans="1:18">
       <c r="A98">
         <v>340</v>
       </c>
       <c r="B98" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="C98">
         <v>2</v>
@@ -4577,15 +5014,18 @@
         <v>0</v>
       </c>
       <c r="I98" s="8" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="99" ht="84" spans="1:9">
+        <v>113</v>
+      </c>
+      <c r="R98">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="99" ht="84" spans="1:18">
       <c r="A99">
         <v>341</v>
       </c>
       <c r="B99" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="C99">
         <v>2</v>
@@ -4606,15 +5046,18 @@
         <v>0</v>
       </c>
       <c r="I99" s="8" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="100" ht="84" spans="1:9">
+        <v>113</v>
+      </c>
+      <c r="R99">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100" ht="84" spans="1:18">
       <c r="A100">
         <v>342</v>
       </c>
       <c r="B100" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="C100">
         <v>2</v>
@@ -4635,7 +5078,10 @@
         <v>0</v>
       </c>
       <c r="I100" s="8" t="s">
-        <v>98</v>
+        <v>113</v>
+      </c>
+      <c r="R100">
+        <v>2</v>
       </c>
     </row>
     <row r="101" spans="9:9">

--- a/Assets/ArtRes/Excel/灵居配置表.xlsx
+++ b/Assets/ArtRes/Excel/灵居配置表.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="117">
   <si>
     <t>id</t>
   </si>
@@ -163,20 +163,28 @@
     <t>被动，会在角色初始添加一些buff，用,分隔</t>
   </si>
   <si>
-    <t>攻击</t>
+    <t>攻击用,分隔</t>
   </si>
   <si>
     <t>工具箱</t>
   </si>
   <si>
-    <t>[攻击]：恢复血量最低的其它队友30血量
-[装甲10]：受到的伤害减10</t>
+    <t>[攻击]：恢复血量最低的其它队友30血量</t>
   </si>
   <si>
     <t>Sfx_Battle_Chequers_Chest_Attack</t>
   </si>
   <si>
     <t>BlizzardPrison</t>
+  </si>
+  <si>
+    <t>SkillPA01</t>
+  </si>
+  <si>
+    <t>[攻击]：恢复血量最低的其它队友40血量</t>
+  </si>
+  <si>
+    <t>[攻击]：恢复血量最低的其它队友50血量</t>
   </si>
   <si>
     <t>扳手</t>
@@ -1376,7 +1384,7 @@
   <cols>
     <col min="9" max="9" width="26.2727272727273" customWidth="1"/>
     <col min="10" max="10" width="14.1818181818182" customWidth="1"/>
-    <col min="12" max="12" width="12.7272727272727" customWidth="1"/>
+    <col min="12" max="12" width="14.0909090909091" customWidth="1"/>
     <col min="13" max="13" width="13.3636363636364" customWidth="1"/>
     <col min="14" max="14" width="11.2727272727273" customWidth="1"/>
     <col min="15" max="15" width="12.7272727272727" customWidth="1"/>
@@ -1384,6 +1392,7 @@
     <col min="17" max="17" width="15.2727272727273" customWidth="1"/>
     <col min="18" max="18" width="12.5454545454545" customWidth="1"/>
     <col min="19" max="19" width="12.8181818181818" customWidth="1"/>
+    <col min="20" max="20" width="10.1818181818182" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20">
@@ -1589,7 +1598,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" ht="42" spans="1:18">
+    <row r="5" ht="28" spans="1:20">
       <c r="A5" s="1">
         <v>10</v>
       </c>
@@ -1603,13 +1612,13 @@
         <v>9</v>
       </c>
       <c r="E5" s="1">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="F5" s="1">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="G5" s="4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H5" s="4">
         <v>20</v>
@@ -1632,8 +1641,14 @@
       <c r="R5">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" ht="42" spans="1:18">
+      <c r="S5">
+        <v>10</v>
+      </c>
+      <c r="T5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" ht="28" spans="1:20">
       <c r="A6" s="1">
         <v>11</v>
       </c>
@@ -1647,19 +1662,19 @@
         <v>9</v>
       </c>
       <c r="E6" s="1">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="F6" s="1">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="G6" s="4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H6" s="4">
         <v>20</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="J6" s="1"/>
       <c r="K6" s="1">
@@ -1676,8 +1691,14 @@
       <c r="R6">
         <v>2</v>
       </c>
-    </row>
-    <row r="7" ht="42" spans="1:18">
+      <c r="S6">
+        <v>11</v>
+      </c>
+      <c r="T6" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" ht="28" spans="1:20">
       <c r="A7" s="1">
         <v>12</v>
       </c>
@@ -1691,19 +1712,19 @@
         <v>9</v>
       </c>
       <c r="E7" s="1">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="F7" s="1">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="G7" s="4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H7" s="4">
         <v>20</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="J7" s="1"/>
       <c r="K7" s="1">
@@ -1720,13 +1741,19 @@
       <c r="R7">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" ht="28" spans="1:18">
+      <c r="S7">
+        <v>12</v>
+      </c>
+      <c r="T7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" ht="28" spans="1:20">
       <c r="A8" s="1">
         <v>20</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C8" s="1">
         <v>2</v>
@@ -1747,7 +1774,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J8" s="1">
         <v>3</v>
@@ -1758,21 +1785,27 @@
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
       <c r="P8" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="Q8" t="s">
         <v>48</v>
       </c>
       <c r="R8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" ht="28" spans="1:18">
+        <v>1</v>
+      </c>
+      <c r="S8">
+        <v>20</v>
+      </c>
+      <c r="T8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" ht="28" spans="1:20">
       <c r="A9" s="1">
         <v>21</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C9" s="1">
         <v>2</v>
@@ -1793,7 +1826,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J9" s="1">
         <v>3</v>
@@ -1804,21 +1837,27 @@
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
       <c r="P9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="Q9" t="s">
         <v>48</v>
       </c>
       <c r="R9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" ht="28" spans="1:18">
+        <v>1</v>
+      </c>
+      <c r="S9">
+        <v>20</v>
+      </c>
+      <c r="T9" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" ht="28" spans="1:20">
       <c r="A10" s="1">
         <v>22</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C10" s="1">
         <v>2</v>
@@ -1839,7 +1878,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J10" s="1">
         <v>3</v>
@@ -1850,21 +1889,27 @@
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
       <c r="P10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="Q10" t="s">
         <v>48</v>
       </c>
       <c r="R10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" ht="28" spans="1:18">
+        <v>1</v>
+      </c>
+      <c r="S10">
+        <v>20</v>
+      </c>
+      <c r="T10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" ht="28" spans="1:20">
       <c r="A11" s="1">
         <v>30</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C11" s="1">
         <v>1</v>
@@ -1885,7 +1930,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="J11" s="1"/>
       <c r="K11" s="1">
@@ -1894,21 +1939,27 @@
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
       <c r="P11" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="Q11" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="R11">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" ht="28" spans="1:18">
+      <c r="S11">
+        <v>30</v>
+      </c>
+      <c r="T11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" ht="28" spans="1:20">
       <c r="A12" s="1">
         <v>31</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C12" s="1">
         <v>1</v>
@@ -1929,7 +1980,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="J12" s="1"/>
       <c r="K12" s="1">
@@ -1938,21 +1989,27 @@
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
       <c r="P12" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="Q12" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="R12">
         <v>2</v>
       </c>
-    </row>
-    <row r="13" ht="28" spans="1:18">
+      <c r="S12">
+        <v>30</v>
+      </c>
+      <c r="T12" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13" ht="28" spans="1:20">
       <c r="A13" s="1">
         <v>32</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C13" s="1">
         <v>1</v>
@@ -1973,7 +2030,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="J13" s="1"/>
       <c r="K13" s="1">
@@ -1982,13 +2039,19 @@
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
       <c r="P13" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="Q13" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="R13">
         <v>2</v>
+      </c>
+      <c r="S13">
+        <v>30</v>
+      </c>
+      <c r="T13" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="14" ht="28" spans="1:18">
@@ -1996,7 +2059,7 @@
         <v>40</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C14" s="1">
         <v>2</v>
@@ -2013,7 +2076,7 @@
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
       <c r="I14" s="4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="J14" s="1"/>
       <c r="K14" s="1">
@@ -2022,7 +2085,7 @@
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
       <c r="Q14" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="R14">
         <v>2</v>
@@ -2033,7 +2096,7 @@
         <v>41</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C15" s="1">
         <v>2</v>
@@ -2050,7 +2113,7 @@
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
       <c r="I15" s="4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="J15" s="1"/>
       <c r="K15" s="1">
@@ -2059,7 +2122,7 @@
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
       <c r="Q15" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="R15">
         <v>2</v>
@@ -2070,7 +2133,7 @@
         <v>42</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C16" s="1">
         <v>2</v>
@@ -2087,7 +2150,7 @@
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="J16" s="1"/>
       <c r="K16" s="1">
@@ -2096,7 +2159,7 @@
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
       <c r="Q16" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="R16">
         <v>2</v>
@@ -2107,7 +2170,7 @@
         <v>50</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C17" s="1">
         <v>4</v>
@@ -2124,7 +2187,7 @@
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
       <c r="I17" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="J17" s="1"/>
       <c r="K17" s="1">
@@ -2141,7 +2204,7 @@
         <v>51</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C18" s="1">
         <v>4</v>
@@ -2158,7 +2221,7 @@
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
       <c r="I18" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="J18" s="1"/>
       <c r="K18" s="1">
@@ -2175,7 +2238,7 @@
         <v>52</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C19" s="1">
         <v>4</v>
@@ -2192,7 +2255,7 @@
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
       <c r="I19" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="J19" s="1"/>
       <c r="K19" s="1">
@@ -2209,7 +2272,7 @@
         <v>60</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C20" s="4">
         <v>3</v>
@@ -2230,7 +2293,7 @@
         <v>0</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="J20" s="1"/>
       <c r="K20" s="1">
@@ -2247,7 +2310,7 @@
         <v>61</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C21" s="1">
         <v>3</v>
@@ -2268,7 +2331,7 @@
         <v>0</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="J21" s="1"/>
       <c r="K21" s="1">
@@ -2285,7 +2348,7 @@
         <v>62</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C22" s="1">
         <v>3</v>
@@ -2306,7 +2369,7 @@
         <v>0</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="J22" s="1"/>
       <c r="K22" s="1">
@@ -2323,7 +2386,7 @@
         <v>70</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C23" s="1">
         <v>5</v>
@@ -2344,7 +2407,7 @@
         <v>0</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="J23" s="1"/>
       <c r="K23" s="1">
@@ -2361,7 +2424,7 @@
         <v>71</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C24" s="1">
         <v>5</v>
@@ -2382,7 +2445,7 @@
         <v>0</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="J24" s="1"/>
       <c r="K24" s="1">
@@ -2399,7 +2462,7 @@
         <v>72</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C25" s="1">
         <v>5</v>
@@ -2420,7 +2483,7 @@
         <v>0</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="J25" s="1"/>
       <c r="K25" s="1">
@@ -2437,7 +2500,7 @@
         <v>80</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C26" s="1">
         <v>1</v>
@@ -2458,7 +2521,7 @@
         <v>0</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="J26" s="1"/>
       <c r="K26" s="1">
@@ -2475,7 +2538,7 @@
         <v>81</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C27" s="1">
         <v>1</v>
@@ -2496,7 +2559,7 @@
         <v>0</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="J27" s="1"/>
       <c r="K27" s="1">
@@ -2513,7 +2576,7 @@
         <v>82</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C28" s="1">
         <v>1</v>
@@ -2534,7 +2597,7 @@
         <v>0</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="J28" s="1"/>
       <c r="K28" s="1">
@@ -2551,7 +2614,7 @@
         <v>90</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C29" s="1">
         <v>1</v>
@@ -2587,7 +2650,7 @@
         <v>91</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C30" s="1">
         <v>1</v>
@@ -2623,7 +2686,7 @@
         <v>92</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C31" s="1">
         <v>1</v>
@@ -2659,7 +2722,7 @@
         <v>100</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
@@ -2683,7 +2746,7 @@
         <v>101</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
@@ -2707,7 +2770,7 @@
         <v>102</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
@@ -2731,7 +2794,7 @@
         <v>110</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C35" s="5">
         <v>1</v>
@@ -2752,7 +2815,7 @@
         <v>0</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="J35" s="1"/>
       <c r="K35" s="1">
@@ -2769,7 +2832,7 @@
         <v>120</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C36" s="5">
         <v>1</v>
@@ -2790,7 +2853,7 @@
         <v>0</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="J36" s="1"/>
       <c r="K36" s="1">
@@ -2807,7 +2870,7 @@
         <v>130</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C37" s="5">
         <v>1</v>
@@ -2828,7 +2891,7 @@
         <v>0</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="J37" s="1"/>
       <c r="K37" s="1">
@@ -2845,7 +2908,7 @@
         <v>140</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C38" s="6">
         <v>2</v>
@@ -2866,7 +2929,7 @@
         <v>0</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
@@ -2881,7 +2944,7 @@
         <v>141</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C39" s="6">
         <v>2</v>
@@ -2902,7 +2965,7 @@
         <v>0</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
@@ -2917,7 +2980,7 @@
         <v>142</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C40" s="6">
         <v>2</v>
@@ -2938,7 +3001,7 @@
         <v>0</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
@@ -2953,7 +3016,7 @@
         <v>150</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C41" s="5">
         <v>3</v>
@@ -2974,7 +3037,7 @@
         <v>50</v>
       </c>
       <c r="I41" s="5" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J41" s="1"/>
       <c r="K41" s="1"/>
@@ -2989,7 +3052,7 @@
         <v>151</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C42" s="5">
         <v>3</v>
@@ -3010,7 +3073,7 @@
         <v>50</v>
       </c>
       <c r="I42" s="5" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
@@ -3025,7 +3088,7 @@
         <v>152</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C43" s="5">
         <v>3</v>
@@ -3046,7 +3109,7 @@
         <v>50</v>
       </c>
       <c r="I43" s="5" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J43" s="1"/>
       <c r="K43" s="1"/>
@@ -3061,7 +3124,7 @@
         <v>160</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C44" s="4">
         <v>1</v>
@@ -3095,7 +3158,7 @@
         <v>161</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C45" s="4">
         <v>1</v>
@@ -3129,7 +3192,7 @@
         <v>162</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C46" s="4">
         <v>1</v>
@@ -3163,7 +3226,7 @@
         <v>170</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C47" s="5">
         <v>1</v>
@@ -3197,7 +3260,7 @@
         <v>171</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C48" s="5">
         <v>1</v>
@@ -3231,7 +3294,7 @@
         <v>172</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C49" s="5">
         <v>1</v>
@@ -3265,7 +3328,7 @@
         <v>180</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C50" s="5">
         <v>2</v>
@@ -3286,7 +3349,7 @@
         <v>0</v>
       </c>
       <c r="I50" s="4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="J50" s="1"/>
       <c r="K50" s="1"/>
@@ -3301,7 +3364,7 @@
         <v>181</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C51" s="5">
         <v>2</v>
@@ -3322,7 +3385,7 @@
         <v>0</v>
       </c>
       <c r="I51" s="4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="J51" s="1"/>
       <c r="K51" s="1"/>
@@ -3337,7 +3400,7 @@
         <v>182</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C52" s="5">
         <v>2</v>
@@ -3358,7 +3421,7 @@
         <v>0</v>
       </c>
       <c r="I52" s="4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
@@ -3373,7 +3436,7 @@
         <v>190</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C53" s="5">
         <v>4</v>
@@ -3394,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="I53" s="5" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="J53" s="1"/>
       <c r="K53" s="1"/>
@@ -3409,7 +3472,7 @@
         <v>191</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C54" s="5">
         <v>4</v>
@@ -3430,7 +3493,7 @@
         <v>0</v>
       </c>
       <c r="I54" s="5" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="J54" s="1"/>
       <c r="K54" s="1"/>
@@ -3445,7 +3508,7 @@
         <v>192</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C55" s="5">
         <v>4</v>
@@ -3466,7 +3529,7 @@
         <v>0</v>
       </c>
       <c r="I55" s="5" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="J55" s="1"/>
       <c r="K55" s="1"/>
@@ -3481,7 +3544,7 @@
         <v>200</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C56" s="4">
         <v>4</v>
@@ -3502,7 +3565,7 @@
         <v>0</v>
       </c>
       <c r="I56" s="4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="J56" s="1"/>
       <c r="K56" s="1"/>
@@ -3517,7 +3580,7 @@
         <v>201</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C57" s="4">
         <v>4</v>
@@ -3538,7 +3601,7 @@
         <v>0</v>
       </c>
       <c r="I57" s="4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="J57" s="1"/>
       <c r="K57" s="1"/>
@@ -3553,7 +3616,7 @@
         <v>202</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C58" s="4">
         <v>4</v>
@@ -3574,7 +3637,7 @@
         <v>0</v>
       </c>
       <c r="I58" s="4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="J58" s="1"/>
       <c r="K58" s="1"/>
@@ -3589,7 +3652,7 @@
         <v>210</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C59" s="5">
         <v>5</v>
@@ -3610,7 +3673,7 @@
         <v>50</v>
       </c>
       <c r="I59" s="4" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="J59" s="1"/>
       <c r="K59" s="1"/>
@@ -3625,7 +3688,7 @@
         <v>211</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C60" s="5">
         <v>5</v>
@@ -3646,7 +3709,7 @@
         <v>50</v>
       </c>
       <c r="I60" s="4" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="J60" s="1"/>
       <c r="K60" s="1"/>
@@ -3661,7 +3724,7 @@
         <v>212</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C61" s="5">
         <v>5</v>
@@ -3682,7 +3745,7 @@
         <v>50</v>
       </c>
       <c r="I61" s="4" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="J61" s="1"/>
       <c r="K61" s="1"/>
@@ -3697,7 +3760,7 @@
         <v>220</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C62" s="5">
         <v>1</v>
@@ -3718,7 +3781,7 @@
         <v>0</v>
       </c>
       <c r="I62" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="J62" s="1"/>
       <c r="K62" s="1"/>
@@ -3733,7 +3796,7 @@
         <v>221</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C63" s="5">
         <v>1</v>
@@ -3754,7 +3817,7 @@
         <v>0</v>
       </c>
       <c r="I63" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="J63" s="1"/>
       <c r="K63" s="1"/>
@@ -3769,7 +3832,7 @@
         <v>222</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C64" s="5">
         <v>1</v>
@@ -3790,7 +3853,7 @@
         <v>0</v>
       </c>
       <c r="I64" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="J64" s="1"/>
       <c r="K64" s="1"/>
@@ -3805,7 +3868,7 @@
         <v>230</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C65" s="5">
         <v>3</v>
@@ -3826,7 +3889,7 @@
         <v>10</v>
       </c>
       <c r="I65" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="J65" s="1"/>
       <c r="K65" s="1"/>
@@ -3841,7 +3904,7 @@
         <v>231</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C66" s="5">
         <v>3</v>
@@ -3862,7 +3925,7 @@
         <v>10</v>
       </c>
       <c r="I66" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="J66" s="1"/>
       <c r="K66" s="1"/>
@@ -3877,7 +3940,7 @@
         <v>232</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C67" s="5">
         <v>3</v>
@@ -3898,7 +3961,7 @@
         <v>10</v>
       </c>
       <c r="I67" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="J67" s="1"/>
       <c r="K67" s="1"/>
@@ -3913,7 +3976,7 @@
         <v>240</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C68" s="5">
         <v>2</v>
@@ -3934,7 +3997,7 @@
         <v>0</v>
       </c>
       <c r="I68" s="4" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="J68" s="1"/>
       <c r="K68" s="1"/>
@@ -3949,7 +4012,7 @@
         <v>241</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C69" s="5">
         <v>2</v>
@@ -3970,7 +4033,7 @@
         <v>0</v>
       </c>
       <c r="I69" s="4" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="J69" s="1"/>
       <c r="K69" s="1"/>
@@ -3985,7 +4048,7 @@
         <v>242</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C70" s="5">
         <v>2</v>
@@ -4006,7 +4069,7 @@
         <v>0</v>
       </c>
       <c r="I70" s="4" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="J70" s="1"/>
       <c r="K70" s="1"/>
@@ -4021,7 +4084,7 @@
         <v>250</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C71" s="4">
         <v>3</v>
@@ -4042,7 +4105,7 @@
         <v>20</v>
       </c>
       <c r="I71" s="4" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="J71" s="1"/>
       <c r="K71" s="1"/>
@@ -4057,7 +4120,7 @@
         <v>251</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C72" s="4">
         <v>3</v>
@@ -4078,7 +4141,7 @@
         <v>20</v>
       </c>
       <c r="I72" s="4" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="J72" s="1"/>
       <c r="K72" s="1"/>
@@ -4093,7 +4156,7 @@
         <v>252</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C73" s="4">
         <v>3</v>
@@ -4114,7 +4177,7 @@
         <v>20</v>
       </c>
       <c r="I73" s="4" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="J73" s="1"/>
       <c r="K73" s="1"/>
@@ -4129,7 +4192,7 @@
         <v>260</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C74" s="4">
         <v>1</v>
@@ -4150,7 +4213,7 @@
         <v>0</v>
       </c>
       <c r="I74" s="4" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="J74" s="1"/>
       <c r="K74" s="1"/>
@@ -4165,7 +4228,7 @@
         <v>261</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C75" s="4">
         <v>1</v>
@@ -4186,7 +4249,7 @@
         <v>0</v>
       </c>
       <c r="I75" s="4" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="J75" s="1"/>
       <c r="K75" s="1"/>
@@ -4201,7 +4264,7 @@
         <v>262</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C76" s="4">
         <v>1</v>
@@ -4222,7 +4285,7 @@
         <v>0</v>
       </c>
       <c r="I76" s="4" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="J76" s="1"/>
       <c r="K76" s="1"/>
@@ -4237,7 +4300,7 @@
         <v>270</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C77" s="4">
         <v>2</v>
@@ -4258,7 +4321,7 @@
         <v>0</v>
       </c>
       <c r="I77" s="4" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="J77" s="1"/>
       <c r="K77" s="1"/>
@@ -4273,7 +4336,7 @@
         <v>271</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C78" s="4">
         <v>2</v>
@@ -4294,7 +4357,7 @@
         <v>0</v>
       </c>
       <c r="I78" s="4" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="J78" s="1"/>
       <c r="K78" s="1"/>
@@ -4309,7 +4372,7 @@
         <v>272</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C79" s="4">
         <v>2</v>
@@ -4330,7 +4393,7 @@
         <v>0</v>
       </c>
       <c r="I79" s="4" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="J79" s="1"/>
       <c r="K79" s="1"/>
@@ -4345,7 +4408,7 @@
         <v>280</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C80" s="4">
         <v>2</v>
@@ -4366,7 +4429,7 @@
         <v>0</v>
       </c>
       <c r="I80" s="4" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="J80" s="1"/>
       <c r="K80" s="1"/>
@@ -4381,7 +4444,7 @@
         <v>281</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C81" s="4">
         <v>2</v>
@@ -4402,7 +4465,7 @@
         <v>0</v>
       </c>
       <c r="I81" s="4" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="J81" s="1"/>
       <c r="K81" s="1"/>
@@ -4417,7 +4480,7 @@
         <v>282</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C82" s="4">
         <v>2</v>
@@ -4438,7 +4501,7 @@
         <v>0</v>
       </c>
       <c r="I82" s="4" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="J82" s="1"/>
       <c r="K82" s="1"/>
@@ -4453,7 +4516,7 @@
         <v>290</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C83" s="4">
         <v>3</v>
@@ -4474,7 +4537,7 @@
         <v>0</v>
       </c>
       <c r="I83" s="4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="J83" s="1"/>
       <c r="K83" s="1"/>
@@ -4489,7 +4552,7 @@
         <v>291</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C84" s="4">
         <v>3</v>
@@ -4510,7 +4573,7 @@
         <v>0</v>
       </c>
       <c r="I84" s="4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="J84" s="1"/>
       <c r="K84" s="1"/>
@@ -4525,7 +4588,7 @@
         <v>292</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C85" s="4">
         <v>3</v>
@@ -4546,7 +4609,7 @@
         <v>0</v>
       </c>
       <c r="I85" s="4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="J85" s="1"/>
       <c r="K85" s="1"/>
@@ -4561,7 +4624,7 @@
         <v>300</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C86" s="5">
         <v>5</v>
@@ -4582,7 +4645,7 @@
         <v>50</v>
       </c>
       <c r="I86" s="4" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="J86" s="1"/>
       <c r="K86" s="1"/>
@@ -4597,7 +4660,7 @@
         <v>301</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C87" s="5">
         <v>5</v>
@@ -4618,7 +4681,7 @@
         <v>50</v>
       </c>
       <c r="I87" s="4" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="J87" s="1"/>
       <c r="K87" s="1"/>
@@ -4633,7 +4696,7 @@
         <v>302</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C88" s="5">
         <v>5</v>
@@ -4654,7 +4717,7 @@
         <v>50</v>
       </c>
       <c r="I88" s="4" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="J88" s="1"/>
       <c r="K88" s="1"/>
@@ -4669,7 +4732,7 @@
         <v>310</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C89" s="5">
         <v>2</v>
@@ -4690,7 +4753,7 @@
         <v>0</v>
       </c>
       <c r="I89" s="4" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="J89" s="1"/>
       <c r="K89" s="1"/>
@@ -4705,7 +4768,7 @@
         <v>311</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C90" s="5">
         <v>2</v>
@@ -4726,7 +4789,7 @@
         <v>0</v>
       </c>
       <c r="I90" s="4" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="J90" s="1"/>
       <c r="K90" s="1"/>
@@ -4741,7 +4804,7 @@
         <v>312</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C91" s="5">
         <v>2</v>
@@ -4762,7 +4825,7 @@
         <v>0</v>
       </c>
       <c r="I91" s="4" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="J91" s="1"/>
       <c r="K91" s="1"/>
@@ -4777,7 +4840,7 @@
         <v>320</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C92" s="5">
         <v>5</v>
@@ -4798,7 +4861,7 @@
         <v>1000</v>
       </c>
       <c r="I92" s="4" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="J92" s="1"/>
       <c r="K92" s="1"/>
@@ -4813,7 +4876,7 @@
         <v>321</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C93" s="5">
         <v>5</v>
@@ -4834,7 +4897,7 @@
         <v>1000</v>
       </c>
       <c r="I93" s="4" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="J93" s="1"/>
       <c r="K93" s="1"/>
@@ -4849,7 +4912,7 @@
         <v>322</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C94" s="5">
         <v>5</v>
@@ -4870,7 +4933,7 @@
         <v>1000</v>
       </c>
       <c r="I94" s="4" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="J94" s="1"/>
       <c r="K94" s="1"/>
@@ -4885,7 +4948,7 @@
         <v>330</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C95" s="5">
         <v>4</v>
@@ -4906,7 +4969,7 @@
         <v>6</v>
       </c>
       <c r="I95" s="4" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="J95" s="1"/>
       <c r="K95" s="1"/>
@@ -4921,7 +4984,7 @@
         <v>331</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C96" s="5">
         <v>4</v>
@@ -4942,7 +5005,7 @@
         <v>6</v>
       </c>
       <c r="I96" s="4" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="J96" s="1"/>
       <c r="K96" s="1"/>
@@ -4957,7 +5020,7 @@
         <v>332</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C97" s="5">
         <v>4</v>
@@ -4978,7 +5041,7 @@
         <v>6</v>
       </c>
       <c r="I97" s="4" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="J97" s="1"/>
       <c r="K97" s="1"/>
@@ -4993,7 +5056,7 @@
         <v>340</v>
       </c>
       <c r="B98" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C98">
         <v>2</v>
@@ -5014,7 +5077,7 @@
         <v>0</v>
       </c>
       <c r="I98" s="8" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="R98">
         <v>2</v>
@@ -5025,7 +5088,7 @@
         <v>341</v>
       </c>
       <c r="B99" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C99">
         <v>2</v>
@@ -5046,7 +5109,7 @@
         <v>0</v>
       </c>
       <c r="I99" s="8" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="R99">
         <v>2</v>
@@ -5057,7 +5120,7 @@
         <v>342</v>
       </c>
       <c r="B100" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C100">
         <v>2</v>
@@ -5078,7 +5141,7 @@
         <v>0</v>
       </c>
       <c r="I100" s="8" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="R100">
         <v>2</v>
